--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_42_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_42_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0814</v>
+        <v>4.8597</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1092</v>
+        <v>2.7867</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9722</v>
+        <v>2.073</v>
       </c>
       <c r="G2" t="n">
         <v>2.6996</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0776</v>
+        <v>0.856</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.4129</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3422</v>
+        <v>0.443</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3536</v>
+        <v>3.8295</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3536</v>
+        <v>1.0312</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.7983</v>
       </c>
       <c r="G3" t="n">
         <v>2.352</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0016</v>
+        <v>0.4775</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4288</v>
+        <v>0.1063</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5729</v>
+        <v>0.3712</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.774</v>
+        <v>3.1758</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6885</v>
+        <v>2.9558</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.2199</v>
       </c>
       <c r="G4" t="n">
         <v>4.2126</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1344</v>
+        <v>0.2673</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2829</v>
+        <v>-0.0156</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1485</v>
+        <v>0.2829</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5416</v>
+        <v>3.1547</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9175</v>
+        <v>1.2281</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6241</v>
+        <v>1.9266</v>
       </c>
       <c r="G5" t="n">
         <v>2.1598</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.742</v>
+        <v>-0.1289</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2161</v>
+        <v>0.0944</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5258</v>
+        <v>-0.2234</v>
       </c>
       <c r="V5" t="n">
         <v>1.3558</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7799</v>
+        <v>1.6892</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6483</v>
+        <v>4.9501</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4282</v>
+        <v>-3.2609</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2729</v>
+        <v>2.6117</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4068</v>
+        <v>-1.6275</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6797</v>
+        <v>4.2392</v>
       </c>
       <c r="J6" t="n">
-        <v>0.101</v>
+        <v>5.1465</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6351</v>
+        <v>0.1176</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7361</v>
+        <v>5.0288</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1719</v>
+        <v>-2.5348</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2283</v>
+        <v>-1.7452</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9436</v>
+        <v>-0.7896</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9709</v>
+        <v>0.3637</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3576</v>
+        <v>0.0356</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3285</v>
+        <v>0.3282</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4734</v>
+        <v>1.6678</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8597</v>
+        <v>-1.4243</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3332</v>
+        <v>3.0921</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5113</v>
+        <v>1.2729</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5438</v>
+        <v>-0.4068</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9675</v>
+        <v>1.6797</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9183</v>
+        <v>0.101</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6301</v>
+        <v>-0.6351</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2882</v>
+        <v>0.7361</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5931</v>
+        <v>1.1719</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0862</v>
+        <v>0.2283</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6793</v>
+        <v>0.9436</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0496</v>
+        <v>0.8588</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-0.1336</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3484</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3861</v>
+        <v>1.2889</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7142</v>
+        <v>-0.7418</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3281</v>
+        <v>2.0307</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6117</v>
+        <v>3.5113</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6275</v>
+        <v>1.5438</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2392</v>
+        <v>1.9675</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1465</v>
+        <v>2.9183</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1176</v>
+        <v>1.6301</v>
       </c>
       <c r="L8" t="n">
-        <v>5.0288</v>
+        <v>1.2882</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5348</v>
+        <v>0.5931</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7452</v>
+        <v>-0.0862</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7896</v>
+        <v>0.6793</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0606</v>
+        <v>-0.1349</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2003</v>
+        <v>-0.1808</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2609</v>
+        <v>0.0459</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2102</v>
+        <v>1.2609</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2492</v>
+        <v>-0.1313</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4594</v>
+        <v>1.3922</v>
       </c>
       <c r="G9" t="n">
         <v>0.07779999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0178</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V9" t="n">
         <v>0.5051</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9043</v>
+        <v>0.97</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2826</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6217</v>
+        <v>0.42</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1617</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2407</v>
+        <v>-0.1751</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.3301</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3567</v>
+        <v>0.1551</v>
       </c>
       <c r="V10" t="n">
         <v>2.0026</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3667</v>
+        <v>-0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3622</v>
+        <v>-3.1695</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9955</v>
+        <v>3.1635</v>
       </c>
       <c r="G11" t="n">
         <v>3.1273</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3009</v>
+        <v>0.0597</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7468</v>
+        <v>-0.5542</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4459</v>
+        <v>0.6139</v>
       </c>
       <c r="V11" t="n">
         <v>1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3178</v>
+        <v>-1.1663</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2789</v>
+        <v>0.3968</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5967</v>
+        <v>-1.5631</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0336</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2842</v>
+        <v>-0.1327</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5678</v>
+        <v>-2.3519</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4309</v>
+        <v>-0.5174</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1369</v>
+        <v>-1.8344</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8728</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0145</v>
+        <v>0.2014</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1968</v>
+        <v>0.1103</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2113</v>
+        <v>0.0912</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.2522</v>
+        <v>18.3723</v>
       </c>
       <c r="E14" t="n">
-        <v>6.794200000000001</v>
+        <v>7.914300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10.4581</v>
+        <v>10.4579</v>
       </c>
       <c r="G14" t="n">
         <v>19.9569</v>
@@ -1534,10 +1534,10 @@
         <v>-3.5448</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3802</v>
+        <v>3.380199999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.7989</v>
+        <v>-5.798900000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-18.5563</v>
@@ -1546,13 +1546,13 @@
         <v>12.7575</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3751</v>
+        <v>2.495</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.6298</v>
+        <v>-0.5097</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0049</v>
+        <v>3.0048</v>
       </c>
       <c r="V14" t="n">
         <v>1.7191</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0101</v>
+        <v>4.3982</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8906</v>
+        <v>4.0086</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1195</v>
+        <v>0.3896</v>
       </c>
       <c r="G15" t="n">
         <v>0.7815</v>
@@ -1624,13 +1624,13 @@
         <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5395</v>
+        <v>-0.1513</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8883</v>
+        <v>-0.7703</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3488</v>
+        <v>0.619</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8683</v>
+        <v>2.3223</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2728</v>
+        <v>1.919</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4045</v>
+        <v>0.4034</v>
       </c>
       <c r="G16" t="n">
         <v>-0.751</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6642</v>
+        <v>-0.2102</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2513</v>
+        <v>-0.6051</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4129</v>
+        <v>0.3949</v>
       </c>
       <c r="V16" t="n">
         <v>1.8919</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1343</v>
+        <v>2.034</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4268</v>
+        <v>2.3535</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2925</v>
+        <v>-0.3195</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5434</v>
+        <v>1.4687</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1753</v>
+        <v>1.683</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.368</v>
+        <v>-0.2143</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0035</v>
+        <v>3.6703</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0035</v>
+        <v>2.2519</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.4184</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-2.2016</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1788</v>
+        <v>-0.5688</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.368</v>
+        <v>-1.6327</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4457</v>
+        <v>0.0138</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4233</v>
+        <v>-0.1571</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0224</v>
+        <v>0.1709</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9052</v>
+        <v>0.2243</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7637</v>
+        <v>0.4832</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8585</v>
+        <v>-0.2589</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4687</v>
+        <v>-0.5434</v>
       </c>
       <c r="H18" t="n">
-        <v>1.683</v>
+        <v>-0.1753</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2143</v>
+        <v>-0.368</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6703</v>
+        <v>0.0035</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2519</v>
+        <v>0.0035</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4184</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2016</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5688</v>
+        <v>-0.1788</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6327</v>
+        <v>-0.368</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1149</v>
+        <v>0.5357</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7468</v>
+        <v>0.4797</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3681</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1657</v>
+        <v>-0.283</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.547</v>
+        <v>-0.4291</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3813</v>
+        <v>0.146</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7715</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1419</v>
+        <v>0.0246</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7393</v>
+        <v>0.5041</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4738</v>
+        <v>-0.5416</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1958</v>
+        <v>-0.4317</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.278</v>
+        <v>-0.1099</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1481</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2104</v>
+        <v>0.1426</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4129</v>
+        <v>0.177</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9439</v>
+        <v>-1.079</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2544</v>
+        <v>0.0185</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1983</v>
+        <v>-1.0975</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9062</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1252</v>
+        <v>-0.2603</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1098</v>
+        <v>-0.3457</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0154</v>
+        <v>0.0854</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9201</v>
+        <v>-2.1639</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0963</v>
+        <v>-1.3852</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1762</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3402</v>
+        <v>-1.3587</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3397</v>
+        <v>0.2004</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0005</v>
+        <v>-1.5591</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3315</v>
+        <v>0.2353</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4887</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1571</v>
+        <v>-0.7127</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0087</v>
+        <v>-1.5941</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.851</v>
+        <v>-0.7477</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1577</v>
+        <v>-0.8464</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3659</v>
+        <v>0.2645</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>-0.3732</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3809</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2836</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.259</v>
+        <v>-2.4312</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9749</v>
+        <v>-2.5065</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2841</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3587</v>
+        <v>-3.3402</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2004</v>
+        <v>-2.3397</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5591</v>
+        <v>-1.0005</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2353</v>
+        <v>-1.3315</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9481000000000001</v>
+        <v>-1.4887</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7127</v>
+        <v>0.1571</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5941</v>
+        <v>-2.0087</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7477</v>
+        <v>-0.851</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8464</v>
+        <v>-1.1577</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8307</v>
+        <v>0.123</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.963</v>
+        <v>-0.1571</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1322</v>
+        <v>0.2801</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1912</v>
+        <v>-5.2824</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5136</v>
+        <v>-4.0625</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6776</v>
+        <v>-1.2199</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8951</v>
+        <v>-5.2914</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3935</v>
+        <v>-3.4177</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2886</v>
+        <v>-1.8737</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8534</v>
+        <v>-2.9541</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4557</v>
+        <v>-3.0277</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7484</v>
+        <v>-2.3373</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0622</v>
+        <v>-0.39</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6862</v>
+        <v>-1.9473</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>0.727</v>
+        <v>0.241</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7591</v>
+        <v>0.0514</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0321</v>
+        <v>0.1896</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.3273</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5519</v>
+        <v>-5.6459</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2984</v>
+        <v>-3.3393</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2535</v>
+        <v>-2.3066</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.2914</v>
+        <v>-1.8951</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.4177</v>
+        <v>0.3935</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8737</v>
+        <v>-2.2886</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.9541</v>
+        <v>0.8534</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.0277</v>
+        <v>1.4557</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0736</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.3373</v>
+        <v>-2.7484</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.39</v>
+        <v>-1.0622</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.9473</v>
+        <v>-1.6862</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>2.7834</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0286</v>
+        <v>0.2724</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1845</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.156</v>
+        <v>0.3389</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-3.3273</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.6645</v>
+        <v>-6.445</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.4404</v>
+        <v>-7.0865</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7759</v>
+        <v>0.6415</v>
       </c>
       <c r="G26" t="n">
         <v>-6.2014</v>
@@ -2482,13 +2482,13 @@
         <v>0.9278</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2311</v>
+        <v>-0.0116</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1123</v>
+        <v>-0.7585</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8812</v>
+        <v>0.7468</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-17.2522</v>
+        <v>-14.8932</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.4581</v>
+        <v>-10.458</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.794099999999999</v>
+        <v>-4.4351</v>
       </c>
       <c r="G27" t="n">
         <v>-19.9568</v>
@@ -2533,10 +2533,10 @@
         <v>-16.2946</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1645999999999983</v>
+        <v>0.1645999999999992</v>
       </c>
       <c r="K27" t="n">
-        <v>3.545100000000001</v>
+        <v>3.5451</v>
       </c>
       <c r="L27" t="n">
         <v>-3.3802</v>
@@ -2551,7 +2551,7 @@
         <v>-12.9144</v>
       </c>
       <c r="P27" t="n">
-        <v>5.7988</v>
+        <v>5.798799999999998</v>
       </c>
       <c r="Q27" t="n">
         <v>-12.7576</v>
@@ -2560,13 +2560,13 @@
         <v>18.5561</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.3751</v>
+        <v>0.9842</v>
       </c>
       <c r="T27" t="n">
         <v>-3.005</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6298</v>
+        <v>3.9888</v>
       </c>
       <c r="V27" t="n">
         <v>-1.719</v>
@@ -2575,7 +2575,7 @@
         <v>5.139600000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.858600000000001</v>
+        <v>-6.858599999999999</v>
       </c>
     </row>
   </sheetData>
